--- a/manufacturing_forms/004_industrial_pneumatic_cylinder_order_form--manufacturing_forms.xlsx
+++ b/manufacturing_forms/004_industrial_pneumatic_cylinder_order_form--manufacturing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>customer_info_page</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>Customer Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>customer_name</t>
+          <t>order_details_page</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>customer_name</t>
+          <t>Order Details</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>quantity_page</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>order_status</t>
+          <t>pressure_page</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>order_status</t>
+          <t>Pressure Rating</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>description_page</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,23 +630,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>cylinder_type_page</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Cylinder Type</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>quantity2_page</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>Quantity2 Page</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>pressure_rating</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pressure_rating</t>
+          <t>Address</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,40 +699,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>order_date</t>
+          <t>order_status_page</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>order_date</t>
+          <t>Order Status</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>cylinder_type</t>
+          <t>contact_info_page</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>cylinder_type</t>
+          <t>Contact Information</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>order_date_page</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Order Date</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,269 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_page</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>customer_name</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>customer_name</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>order_date</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>order_date</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>cylinder_type</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>cylinder_type</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>contact_email</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>contact_email</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>customer_name</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>customer_name</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>address</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>address</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>order_status</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>order_status</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1052,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1080,204 +827,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>order_status_choices</t>
+          <t>cylinder_type_page_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'in_progress'}</t>
+          <t>type_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'In Progress'}</t>
+          <t>Type 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>order_status_choices</t>
+          <t>cylinder_type_page_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'in_warehouse'}</t>
+          <t>type_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'In Warehouse'}</t>
+          <t>Type 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>order_status_choices</t>
+          <t>cylinder_type_page_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'shipped'}</t>
+          <t>type_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Shipped'}</t>
+          <t>Type 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cylinder_type_choices</t>
+          <t>order_status_page_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'type_1'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Type 1'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cylinder_type_choices</t>
+          <t>order_status_page_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'type_2'}</t>
+          <t>in_warehouse</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Type 2'}</t>
+          <t>In Warehouse</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cylinder_type_choices</t>
+          <t>order_status_page_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'type_3'}</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Type 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cylinder_type_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'type_1'}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'Type 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cylinder_type_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'type_2'}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'Type 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cylinder_type_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'type_3'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'Type 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>order_status_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'in_progress'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'In Progress'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>order_status_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'in_warehouse'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'In Warehouse'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>order_status_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'shipped'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'Shipped'}</t>
+          <t>Shipped</t>
         </is>
       </c>
     </row>
